--- a/config/food-catalog.xlsx
+++ b/config/food-catalog.xlsx
@@ -1106,8 +1106,10 @@
       <ns0:c r="F2" s="2" t="str">
         <ns0:v>city-01-beijing-BeiJingKaoYa.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G2" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-01-beijing/city-01-beijing-BeiJingKaoYa.png</ns0:v>
+      <ns0:c r="G2" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-01-beijing/city-01-beijing-BeiJingKaoYa.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H2" s="2" t="str">
         <ns0:v>c0d94ecc-2135-436c-b9db-07f5586c5b43</ns0:v>
@@ -1141,8 +1143,10 @@
       <ns0:c r="F3" s="2" t="str">
         <ns0:v>city-01-beijing-ShuanYangRou.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G3" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-01-beijing/city-01-beijing-ShuanYangRou.png</ns0:v>
+      <ns0:c r="G3" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-01-beijing/city-01-beijing-ShuanYangRou.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H3" s="2" t="str">
         <ns0:v>40435846-ae96-466a-8164-4a70e9b0132f</ns0:v>
@@ -1176,8 +1180,10 @@
       <ns0:c r="F4" s="2" t="str">
         <ns0:v>city-01-beijing-ZhaJiangMian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G4" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-01-beijing/city-01-beijing-ZhaJiangMian.png</ns0:v>
+      <ns0:c r="G4" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-01-beijing/city-01-beijing-ZhaJiangMian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H4" s="2" t="str">
         <ns0:v>9ec00fe5-0a45-4bb7-86fc-46d58cb803f5</ns0:v>
@@ -1211,8 +1217,10 @@
       <ns0:c r="F5" s="2" t="str">
         <ns0:v>city-01-beijing-LuZhuHuoShao.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G5" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-01-beijing/city-01-beijing-LuZhuHuoShao.png</ns0:v>
+      <ns0:c r="G5" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-01-beijing/city-01-beijing-LuZhuHuoShao.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H5" s="2" t="str">
         <ns0:v>e8552870-bf5f-45b7-a965-384e0c22528c</ns0:v>
@@ -1246,8 +1254,10 @@
       <ns0:c r="F6" s="2" t="str">
         <ns0:v>city-01-beijing-DouZhiJiaoQuan.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G6" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-01-beijing/city-01-beijing-DouZhiJiaoQuan.png</ns0:v>
+      <ns0:c r="G6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-01-beijing/city-01-beijing-DouZhiJiaoQuan.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H6" s="2" t="str">
         <ns0:v>a05a7cdc-0101-4122-85f3-736021e416bd</ns0:v>
@@ -1281,8 +1291,10 @@
       <ns0:c r="F7" s="2" t="str">
         <ns0:v>city-02-shanghai-NanJingXiaoLongBao.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G7" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-02-shanghai/city-02-shanghai-NanJingXiaoLongBao.png</ns0:v>
+      <ns0:c r="G7" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-02-shanghai/city-02-shanghai-NanJingXiaoLongBao.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H7" s="2" t="str">
         <ns0:v>d3718177-95c3-417e-aad8-dc56f3c8a9e7</ns0:v>
@@ -1316,8 +1328,10 @@
       <ns0:c r="F8" s="2" t="str">
         <ns0:v>city-02-shanghai-BenBangHongShaoRou.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G8" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-02-shanghai/city-02-shanghai-BenBangHongShaoRou.png</ns0:v>
+      <ns0:c r="G8" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-02-shanghai/city-02-shanghai-BenBangHongShaoRou.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H8" s="2" t="str">
         <ns0:v>579bac3b-c75e-4d64-ab5c-981033b71bd1</ns0:v>
@@ -1351,8 +1365,10 @@
       <ns0:c r="F9" s="2" t="str">
         <ns0:v>city-02-shanghai-YanDuXian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G9" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-02-shanghai/city-02-shanghai-YanDuXian.png</ns0:v>
+      <ns0:c r="G9" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-02-shanghai/city-02-shanghai-YanDuXian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H9" s="2" t="str">
         <ns0:v>cba1ed80-5f72-47c8-9615-2b94e3ca0bcb</ns0:v>
@@ -1386,8 +1402,10 @@
       <ns0:c r="F10" s="2" t="str">
         <ns0:v>city-02-shanghai-CaoTouQuanZi.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G10" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-02-shanghai/city-02-shanghai-CaoTouQuanZi.png</ns0:v>
+      <ns0:c r="G10" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-02-shanghai/city-02-shanghai-CaoTouQuanZi.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H10" s="2" t="str">
         <ns0:v>f8c41a3e-aa5c-484a-919a-be47b3ecd95b</ns0:v>
@@ -1421,8 +1439,10 @@
       <ns0:c r="F11" s="2" t="str">
         <ns0:v>city-02-shanghai-BaBaoLaJiang.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G11" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-02-shanghai/city-02-shanghai-BaBaoLaJiang.png</ns0:v>
+      <ns0:c r="G11" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-02-shanghai/city-02-shanghai-BaBaoLaJiang.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H11" s="2" t="str">
         <ns0:v>bf9210fb-d15a-4cdd-b0ba-29655c4a0212</ns0:v>
@@ -1456,8 +1476,10 @@
       <ns0:c r="F12" s="2" t="str">
         <ns0:v>city-03-nanjing-YanShuiYa.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G12" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-03-nanjing/city-03-nanjing-YanShuiYa.png</ns0:v>
+      <ns0:c r="G12" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-03-nanjing/city-03-nanjing-YanShuiYa.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H12" s="2" t="str">
         <ns0:v>1de4783a-aa5a-406b-a9dd-fc8905dd4bca</ns0:v>
@@ -1491,8 +1513,10 @@
       <ns0:c r="F13" s="2" t="str">
         <ns0:v>city-03-nanjing-GuiHuaTangYuMiao.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G13" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-03-nanjing/city-03-nanjing-GuiHuaTangYuMiao.png</ns0:v>
+      <ns0:c r="G13" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-03-nanjing/city-03-nanjing-GuiHuaTangYuMiao.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H13" s="2" t="str">
         <ns0:v>41d807ec-764a-49b4-b497-47d033b351b1</ns0:v>
@@ -1526,8 +1550,10 @@
       <ns0:c r="F14" s="2" t="str">
         <ns0:v>city-03-nanjing-JinLingKaoYa.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G14" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-03-nanjing/city-03-nanjing-JinLingKaoYa.png</ns0:v>
+      <ns0:c r="G14" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-03-nanjing/city-03-nanjing-JinLingKaoYa.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H14" s="2" t="str">
         <ns0:v>14097620-5ecc-4ad5-8ffe-db29c5d7d3ba</ns0:v>
@@ -1561,8 +1587,10 @@
       <ns0:c r="F15" s="2" t="str">
         <ns0:v>city-03-nanjing-NiuRouGuoTie.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G15" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-03-nanjing/city-03-nanjing-NiuRouGuoTie.png</ns0:v>
+      <ns0:c r="G15" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-03-nanjing/city-03-nanjing-NiuRouGuoTie.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H15" s="2" t="str">
         <ns0:v>c246dd51-28ca-49cf-bd7d-2fd3e7cb22af</ns0:v>
@@ -1596,8 +1624,10 @@
       <ns0:c r="F16" s="2" t="str">
         <ns0:v>city-03-nanjing-YaXueFenSiTang.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G16" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-03-nanjing/city-03-nanjing-YaXueFenSiTang.png</ns0:v>
+      <ns0:c r="G16" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-03-nanjing/city-03-nanjing-YaXueFenSiTang.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H16" s="2" t="str">
         <ns0:v>865592e4-0079-4d90-b042-0a0b9fedf66d</ns0:v>
@@ -1631,8 +1661,10 @@
       <ns0:c r="F17" s="2" t="str">
         <ns0:v>city-04-xiamen-ShaChaMian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G17" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-04-xiamen/city-04-xiamen-ShaChaMian.png</ns0:v>
+      <ns0:c r="G17" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-04-xiamen/city-04-xiamen-ShaChaMian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H17" s="2" t="str">
         <ns0:v>9e753a4e-be29-4d9a-9c84-aaa6b870d5f4</ns0:v>
@@ -1666,8 +1698,10 @@
       <ns0:c r="F18" s="2" t="str">
         <ns0:v>city-04-xiamen-TuSunDong.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G18" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-04-xiamen/city-04-xiamen-TuSunDong.png</ns0:v>
+      <ns0:c r="G18" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-04-xiamen/city-04-xiamen-TuSunDong.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H18" s="2" t="str">
         <ns0:v>97ceac68-fa79-4a76-98a3-f18d188a202d</ns0:v>
@@ -1701,8 +1735,10 @@
       <ns0:c r="F19" s="2" t="str">
         <ns0:v>city-04-xiamen-JiangMuYa.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G19" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-04-xiamen/city-04-xiamen-JiangMuYa.png</ns0:v>
+      <ns0:c r="G19" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-04-xiamen/city-04-xiamen-JiangMuYa.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H19" s="2" t="str">
         <ns0:v>470c76bd-9570-40f2-adc9-717fe24bceec</ns0:v>
@@ -1736,8 +1772,10 @@
       <ns0:c r="F20" s="2" t="str">
         <ns0:v>city-04-xiamen-HaiLiJian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G20" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-04-xiamen/city-04-xiamen-HaiLiJian.png</ns0:v>
+      <ns0:c r="G20" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-04-xiamen/city-04-xiamen-HaiLiJian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H20" s="2" t="str">
         <ns0:v>04bebf98-ed6a-45c1-88c4-cca61269bb89</ns0:v>
@@ -1771,8 +1809,10 @@
       <ns0:c r="F21" s="2" t="str">
         <ns0:v>city-04-xiamen-HuaShengTang.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G21" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-04-xiamen/city-04-xiamen-HuaShengTang.png</ns0:v>
+      <ns0:c r="G21" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-04-xiamen/city-04-xiamen-HuaShengTang.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H21" s="2" t="str">
         <ns0:v>f2d733b0-0b3a-4ce9-969a-0f1e557e9638</ns0:v>
@@ -1808,8 +1848,10 @@
       <ns0:c r="F22" s="2" t="str">
         <ns0:v>city-05-changsha-ChangShaMiXian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G22" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-05-changsha/city-05-changsha-ChangShaMiXian.png</ns0:v>
+      <ns0:c r="G22" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-05-changsha/city-05-changsha-ChangShaMiXian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H22" s="2" t="str">
         <ns0:v>2c721c26-1126-4da0-83d6-920a72b194e8</ns0:v>
@@ -1843,8 +1885,10 @@
       <ns0:c r="F23" s="2" t="str">
         <ns0:v>city-05-changsha-ChouDouFu.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G23" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-05-changsha/city-05-changsha-ChouDouFu.png</ns0:v>
+      <ns0:c r="G23" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-05-changsha/city-05-changsha-ChouDouFu.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H23" s="2" t="str">
         <ns0:v>53c0d115-94fb-4583-a736-075f1339d310</ns0:v>
@@ -1880,8 +1924,10 @@
       <ns0:c r="F24" s="2" t="str">
         <ns0:v>city-05-changsha-DuoJiaoYuTou.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G24" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-05-changsha/city-05-changsha-DuoJiaoYuTou.png</ns0:v>
+      <ns0:c r="G24" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-05-changsha/city-05-changsha-DuoJiaoYuTou.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H24" s="2" t="str">
         <ns0:v>ce3878c1-424a-419a-857f-df020cbf4b6e</ns0:v>
@@ -1917,8 +1963,10 @@
       <ns0:c r="F25" s="2" t="str">
         <ns0:v>city-05-changsha-KouWeiXia.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G25" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-05-changsha/city-05-changsha-KouWeiXia.png</ns0:v>
+      <ns0:c r="G25" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-05-changsha/city-05-changsha-KouWeiXia.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H25" s="2" t="str">
         <ns0:v>f245c54a-357c-4ef1-83ee-4ea7851508d5</ns0:v>
@@ -1954,8 +2002,10 @@
       <ns0:c r="F26" s="2" t="str">
         <ns0:v>city-05-changsha-TangYouBaBa.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G26" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-05-changsha/city-05-changsha-TangYouBaBa.png</ns0:v>
+      <ns0:c r="G26" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-05-changsha/city-05-changsha-TangYouBaBa.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H26" s="2" t="str">
         <ns0:v>8455e619-b029-4518-87fa-4c3d872cd87a</ns0:v>
@@ -1989,8 +2039,10 @@
       <ns0:c r="F27" s="2" t="str">
         <ns0:v>city-06-guangzhou-BaiQieJi.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G27" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-06-guangzhou/city-06-guangzhou-BaiQieJi.png</ns0:v>
+      <ns0:c r="G27" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-06-guangzhou/city-06-guangzhou-BaiQieJi.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H27" s="2" t="str">
         <ns0:v>06793353-094e-48e1-b4bd-031f3a03fe19</ns0:v>
@@ -2026,8 +2078,10 @@
       <ns0:c r="F28" s="2" t="str">
         <ns0:v>city-06-guangzhou-ChangFen.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G28" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-06-guangzhou/city-06-guangzhou-ChangFen.png</ns0:v>
+      <ns0:c r="G28" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-06-guangzhou/city-06-guangzhou-ChangFen.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H28" s="2" t="str">
         <ns0:v>7c7a9ee2-6c6b-4c31-abce-11ea2840f36c</ns0:v>
@@ -2063,8 +2117,10 @@
       <ns0:c r="F29" s="2" t="str">
         <ns0:v>city-06-guangzhou-ChaShao.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G29" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-06-guangzhou/city-06-guangzhou-ChaShao.png</ns0:v>
+      <ns0:c r="G29" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-06-guangzhou/city-06-guangzhou-ChaShao.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H29" s="2" t="str">
         <ns0:v>7b914314-9684-406c-85be-3ccd74d8592b</ns0:v>
@@ -2098,8 +2154,10 @@
       <ns0:c r="F30" s="2" t="str">
         <ns0:v>city-06-guangzhou-GanChaoNiuHe.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G30" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-06-guangzhou/city-06-guangzhou-GanChaoNiuHe.png</ns0:v>
+      <ns0:c r="G30" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-06-guangzhou/city-06-guangzhou-GanChaoNiuHe.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H30" s="2" t="str">
         <ns0:v>69abb585-c79d-4d5a-b780-3695b93716be</ns0:v>
@@ -2133,8 +2191,10 @@
       <ns0:c r="F31" s="2" t="str">
         <ns0:v>city-06-guangzhou-TingZaiZhou.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G31" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-06-guangzhou/city-06-guangzhou-TingZaiZhou.png</ns0:v>
+      <ns0:c r="G31" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-06-guangzhou/city-06-guangzhou-TingZaiZhou.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H31" s="2" t="str">
         <ns0:v>2428cd07-bcaa-43c5-ab53-7c1e49bf5bcf</ns0:v>
@@ -2170,8 +2230,10 @@
       <ns0:c r="F32" s="2" t="str">
         <ns0:v>city-07-chengdu-HuiGuoRou.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G32" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-07-chengdu/city-07-chengdu-HuiGuoRou.png</ns0:v>
+      <ns0:c r="G32" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-07-chengdu/city-07-chengdu-HuiGuoRou.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H32" s="2" t="str">
         <ns0:v>3d761d6b-f995-4eb2-8b1c-ee33ac328f8d</ns0:v>
@@ -2209,8 +2271,10 @@
       <ns0:c r="F33" s="2" t="str">
         <ns0:v>city-07-chengdu-FuQiFeiPian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G33" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-07-chengdu/city-07-chengdu-FuQiFeiPian.png</ns0:v>
+      <ns0:c r="G33" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-07-chengdu/city-07-chengdu-FuQiFeiPian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H33" s="2" t="str">
         <ns0:v>3d6be629-f92e-49bc-af5a-15263f553e49</ns0:v>
@@ -2248,8 +2312,10 @@
       <ns0:c r="F34" s="2" t="str">
         <ns0:v>city-07-chengdu-MaPoDouFu.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G34" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-07-chengdu/city-07-chengdu-MaPoDouFu.png</ns0:v>
+      <ns0:c r="G34" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-07-chengdu/city-07-chengdu-MaPoDouFu.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H34" s="2" t="str">
         <ns0:v>edd4649b-e09c-4922-b431-7525b5dac15b</ns0:v>
@@ -2287,8 +2353,10 @@
       <ns0:c r="F35" s="2" t="str">
         <ns0:v>city-07-chengdu-DanDanMian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G35" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-07-chengdu/city-07-chengdu-DanDanMian.png</ns0:v>
+      <ns0:c r="G35" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-07-chengdu/city-07-chengdu-DanDanMian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H35" s="2" t="str">
         <ns0:v>02e5f9cf-20e3-40b9-bcee-9ffb0ca1283e</ns0:v>
@@ -2326,8 +2394,10 @@
       <ns0:c r="F36" s="2" t="str">
         <ns0:v>city-07-chengdu-LongChaoShou.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G36" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-07-chengdu/city-07-chengdu-LongChaoShou.png</ns0:v>
+      <ns0:c r="G36" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-07-chengdu/city-07-chengdu-LongChaoShou.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H36" s="2" t="str">
         <ns0:v>a43d8fd8-f1d0-4125-9073-a0aa0a95433a</ns0:v>
@@ -2365,8 +2435,10 @@
       <ns0:c r="F37" s="2" t="str">
         <ns0:v>city-08-xian-NiuYangRouPaoMo.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G37" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-08-xian/city-08-xian-NiuYangRouPaoMo.png</ns0:v>
+      <ns0:c r="G37" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-08-xian/city-08-xian-NiuYangRouPaoMo.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H37" s="2" t="str">
         <ns0:v>d8befafb-0f4a-4434-a32f-e5a70836f24c</ns0:v>
@@ -2404,8 +2476,10 @@
       <ns0:c r="F38" s="2" t="str">
         <ns0:v>city-08-xian-RouWanHuLaTang.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G38" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-08-xian/city-08-xian-RouWanHuLaTang.png</ns0:v>
+      <ns0:c r="G38" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-08-xian/city-08-xian-RouWanHuLaTang.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H38" s="2" t="str">
         <ns0:v>506e3e46-5a6d-49d5-8d12-a05e2a9bf6d5</ns0:v>
@@ -2443,8 +2517,10 @@
       <ns0:c r="F39" s="2" t="str">
         <ns0:v>city-08-xian-RouJiaMo.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G39" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-08-xian/city-08-xian-RouJiaMo.png</ns0:v>
+      <ns0:c r="G39" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-08-xian/city-08-xian-RouJiaMo.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H39" s="2" t="str">
         <ns0:v>fbaf427b-0275-4359-b9bd-94d28928ee7d</ns0:v>
@@ -2482,8 +2558,10 @@
       <ns0:c r="F40" s="2" t="str">
         <ns0:v>city-08-xian-HuLuJi.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G40" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-08-xian/city-08-xian-HuLuJi.png</ns0:v>
+      <ns0:c r="G40" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-08-xian/city-08-xian-HuLuJi.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H40" s="2" t="str">
         <ns0:v>2a59dff9-758c-433d-96ee-5fe05f0bb6ff</ns0:v>
@@ -2521,8 +2599,10 @@
       <ns0:c r="F41" s="2" t="str">
         <ns0:v>city-08-xian-BiangbiangMian.png</ns0:v>
       </ns0:c>
-      <ns0:c r="G41" s="2" t="str">
-        <ns0:v>assets/Bundle/levels/city-08-xian/city-08-xian-BiangbiangMian.png</ns0:v>
+      <ns0:c r="G41" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>assets/Bundle/thumbnails/city-08-xian/city-08-xian-BiangbiangMian.png</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H41" s="2" t="str">
         <ns0:v>2202379f-b9b0-4c3d-aab2-5aab32ac8e70</ns0:v>

--- a/config/food-catalog.xlsx
+++ b/config/food-catalog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="美食配置" sheetId="1" r:id="Ra1759d97539349ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="美食配置" sheetId="1" r:id="Rdb063465d6e64b93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1107,7 +1107,7 @@
         <x:v>city-02-beijing-BeiJingKaoYa.png</x:v>
       </x:c>
       <x:c r="G2" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-02-beijing/city-02-beijing-BeiJingKaoYa.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-02-beijing/city-02-beijing-BeiJingKaoYa.png</x:v>
       </x:c>
       <x:c r="H2" s="2" t="str">
         <x:v>c0d94ecc-2135-436c-b9db-07f5586c5b43</x:v>
@@ -1142,7 +1142,7 @@
         <x:v>city-02-beijing-ShuanYangRou.png</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-02-beijing/city-02-beijing-ShuanYangRou.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-02-beijing/city-02-beijing-ShuanYangRou.png</x:v>
       </x:c>
       <x:c r="H3" s="2" t="str">
         <x:v>40435846-ae96-466a-8164-4a70e9b0132f</x:v>
@@ -1177,7 +1177,7 @@
         <x:v>city-02-beijing-ZhaJiangMian.png</x:v>
       </x:c>
       <x:c r="G4" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-02-beijing/city-02-beijing-ZhaJiangMian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-02-beijing/city-02-beijing-ZhaJiangMian.png</x:v>
       </x:c>
       <x:c r="H4" s="2" t="str">
         <x:v>9ec00fe5-0a45-4bb7-86fc-46d58cb803f5</x:v>
@@ -1212,7 +1212,7 @@
         <x:v>city-02-beijing-LuZhuHuoShao.png</x:v>
       </x:c>
       <x:c r="G5" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-02-beijing/city-02-beijing-LuZhuHuoShao.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-02-beijing/city-02-beijing-LuZhuHuoShao.png</x:v>
       </x:c>
       <x:c r="H5" s="2" t="str">
         <x:v>e8552870-bf5f-45b7-a965-384e0c22528c</x:v>
@@ -1247,7 +1247,7 @@
         <x:v>city-02-beijing-DouZhiJiaoQuan.png</x:v>
       </x:c>
       <x:c r="G6" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-02-beijing/city-02-beijing-DouZhiJiaoQuan.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-02-beijing/city-02-beijing-DouZhiJiaoQuan.png</x:v>
       </x:c>
       <x:c r="H6" s="2" t="str">
         <x:v>a05a7cdc-0101-4122-85f3-736021e416bd</x:v>
@@ -1282,7 +1282,7 @@
         <x:v>city-03-shanghai-NanJingXiaoLongBao.png</x:v>
       </x:c>
       <x:c r="G7" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-03-shanghai/city-03-shanghai-NanJingXiaoLongBao.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-03-shanghai/city-03-shanghai-NanJingXiaoLongBao.png</x:v>
       </x:c>
       <x:c r="H7" s="2" t="str">
         <x:v>d3718177-95c3-417e-aad8-dc56f3c8a9e7</x:v>
@@ -1317,7 +1317,7 @@
         <x:v>city-03-shanghai-BenBangHongShaoRou.png</x:v>
       </x:c>
       <x:c r="G8" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-03-shanghai/city-03-shanghai-BenBangHongShaoRou.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-03-shanghai/city-03-shanghai-BenBangHongShaoRou.png</x:v>
       </x:c>
       <x:c r="H8" s="2" t="str">
         <x:v>579bac3b-c75e-4d64-ab5c-981033b71bd1</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>city-03-shanghai-YanDuXian.png</x:v>
       </x:c>
       <x:c r="G9" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-03-shanghai/city-03-shanghai-YanDuXian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-03-shanghai/city-03-shanghai-YanDuXian.png</x:v>
       </x:c>
       <x:c r="H9" s="2" t="str">
         <x:v>cba1ed80-5f72-47c8-9615-2b94e3ca0bcb</x:v>
@@ -1387,7 +1387,7 @@
         <x:v>city-03-shanghai-CaoTouQuanZi.png</x:v>
       </x:c>
       <x:c r="G10" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-03-shanghai/city-03-shanghai-CaoTouQuanZi.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-03-shanghai/city-03-shanghai-CaoTouQuanZi.png</x:v>
       </x:c>
       <x:c r="H10" s="2" t="str">
         <x:v>f8c41a3e-aa5c-484a-919a-be47b3ecd95b</x:v>
@@ -1422,7 +1422,7 @@
         <x:v>city-03-shanghai-BaBaoLaJiang.png</x:v>
       </x:c>
       <x:c r="G11" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-03-shanghai/city-03-shanghai-BaBaoLaJiang.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-03-shanghai/city-03-shanghai-BaBaoLaJiang.png</x:v>
       </x:c>
       <x:c r="H11" s="2" t="str">
         <x:v>bf9210fb-d15a-4cdd-b0ba-29655c4a0212</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>city-04-nanjing-YanShuiYa.png</x:v>
       </x:c>
       <x:c r="G12" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-04-nanjing/city-04-nanjing-YanShuiYa.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-04-nanjing/city-04-nanjing-YanShuiYa.png</x:v>
       </x:c>
       <x:c r="H12" s="2" t="str">
         <x:v>1de4783a-aa5a-406b-a9dd-fc8905dd4bca</x:v>
@@ -1492,7 +1492,7 @@
         <x:v>city-04-nanjing-GuiHuaTangYuMiao.png</x:v>
       </x:c>
       <x:c r="G13" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-04-nanjing/city-04-nanjing-GuiHuaTangYuMiao.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-04-nanjing/city-04-nanjing-GuiHuaTangYuMiao.png</x:v>
       </x:c>
       <x:c r="H13" s="2" t="str">
         <x:v>41d807ec-764a-49b4-b497-47d033b351b1</x:v>
@@ -1527,7 +1527,7 @@
         <x:v>city-04-nanjing-JinLingKaoYa.png</x:v>
       </x:c>
       <x:c r="G14" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-04-nanjing/city-04-nanjing-JinLingKaoYa.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-04-nanjing/city-04-nanjing-JinLingKaoYa.png</x:v>
       </x:c>
       <x:c r="H14" s="2" t="str">
         <x:v>14097620-5ecc-4ad5-8ffe-db29c5d7d3ba</x:v>
@@ -1562,7 +1562,7 @@
         <x:v>city-04-nanjing-NiuRouGuoTie.png</x:v>
       </x:c>
       <x:c r="G15" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-04-nanjing/city-04-nanjing-NiuRouGuoTie.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-04-nanjing/city-04-nanjing-NiuRouGuoTie.png</x:v>
       </x:c>
       <x:c r="H15" s="2" t="str">
         <x:v>c246dd51-28ca-49cf-bd7d-2fd3e7cb22af</x:v>
@@ -1597,7 +1597,7 @@
         <x:v>city-04-nanjing-YaXueFenSiTang.png</x:v>
       </x:c>
       <x:c r="G16" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-04-nanjing/city-04-nanjing-YaXueFenSiTang.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-04-nanjing/city-04-nanjing-YaXueFenSiTang.png</x:v>
       </x:c>
       <x:c r="H16" s="2" t="str">
         <x:v>865592e4-0079-4d90-b042-0a0b9fedf66d</x:v>
@@ -1632,7 +1632,7 @@
         <x:v>city-05-xiamen-ShaChaMian.png</x:v>
       </x:c>
       <x:c r="G17" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-05-xiamen/city-05-xiamen-ShaChaMian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-05-xiamen/city-05-xiamen-ShaChaMian.png</x:v>
       </x:c>
       <x:c r="H17" s="2" t="str">
         <x:v>9e753a4e-be29-4d9a-9c84-aaa6b870d5f4</x:v>
@@ -1667,7 +1667,7 @@
         <x:v>city-05-xiamen-TuSunDong.png</x:v>
       </x:c>
       <x:c r="G18" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-05-xiamen/city-05-xiamen-TuSunDong.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-05-xiamen/city-05-xiamen-TuSunDong.png</x:v>
       </x:c>
       <x:c r="H18" s="2" t="str">
         <x:v>97ceac68-fa79-4a76-98a3-f18d188a202d</x:v>
@@ -1702,7 +1702,7 @@
         <x:v>city-05-xiamen-JiangMuYa.png</x:v>
       </x:c>
       <x:c r="G19" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-05-xiamen/city-05-xiamen-JiangMuYa.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-05-xiamen/city-05-xiamen-JiangMuYa.png</x:v>
       </x:c>
       <x:c r="H19" s="2" t="str">
         <x:v>470c76bd-9570-40f2-adc9-717fe24bceec</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>city-05-xiamen-HaiLiJian.png</x:v>
       </x:c>
       <x:c r="G20" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-05-xiamen/city-05-xiamen-HaiLiJian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-05-xiamen/city-05-xiamen-HaiLiJian.png</x:v>
       </x:c>
       <x:c r="H20" s="2" t="str">
         <x:v>04bebf98-ed6a-45c1-88c4-cca61269bb89</x:v>
@@ -1772,7 +1772,7 @@
         <x:v>city-05-xiamen-HuaShengTang.png</x:v>
       </x:c>
       <x:c r="G21" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-05-xiamen/city-05-xiamen-HuaShengTang.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-05-xiamen/city-05-xiamen-HuaShengTang.png</x:v>
       </x:c>
       <x:c r="H21" s="2" t="str">
         <x:v>f2d733b0-0b3a-4ce9-969a-0f1e557e9638</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>city-06-changsha-ChangShaMiXian.png</x:v>
       </x:c>
       <x:c r="G22" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-06-changsha/city-06-changsha-ChangShaMiXian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-06-changsha/city-06-changsha-ChangShaMiXian.png</x:v>
       </x:c>
       <x:c r="H22" s="2" t="str">
         <x:v>2c721c26-1126-4da0-83d6-920a72b194e8</x:v>
@@ -1844,7 +1844,7 @@
         <x:v>city-06-changsha-ChouDouFu.png</x:v>
       </x:c>
       <x:c r="G23" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-06-changsha/city-06-changsha-ChouDouFu.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-06-changsha/city-06-changsha-ChouDouFu.png</x:v>
       </x:c>
       <x:c r="H23" s="2" t="str">
         <x:v>53c0d115-94fb-4583-a736-075f1339d310</x:v>
@@ -1881,7 +1881,7 @@
         <x:v>city-06-changsha-DuoJiaoYuTou.png</x:v>
       </x:c>
       <x:c r="G24" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-06-changsha/city-06-changsha-DuoJiaoYuTou.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-06-changsha/city-06-changsha-DuoJiaoYuTou.png</x:v>
       </x:c>
       <x:c r="H24" s="2" t="str">
         <x:v>ce3878c1-424a-419a-857f-df020cbf4b6e</x:v>
@@ -1918,7 +1918,7 @@
         <x:v>city-06-changsha-KouWeiXia.png</x:v>
       </x:c>
       <x:c r="G25" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-06-changsha/city-06-changsha-KouWeiXia.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-06-changsha/city-06-changsha-KouWeiXia.png</x:v>
       </x:c>
       <x:c r="H25" s="2" t="str">
         <x:v>f245c54a-357c-4ef1-83ee-4ea7851508d5</x:v>
@@ -1955,7 +1955,7 @@
         <x:v>city-06-changsha-TangYouBaBa.png</x:v>
       </x:c>
       <x:c r="G26" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-06-changsha/city-06-changsha-TangYouBaBa.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-06-changsha/city-06-changsha-TangYouBaBa.png</x:v>
       </x:c>
       <x:c r="H26" s="2" t="str">
         <x:v>8455e619-b029-4518-87fa-4c3d872cd87a</x:v>
@@ -1990,7 +1990,7 @@
         <x:v>city-07-guangzhou-BaiQieJi.png</x:v>
       </x:c>
       <x:c r="G27" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-07-guangzhou/city-07-guangzhou-BaiQieJi.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-07-guangzhou/city-07-guangzhou-BaiQieJi.png</x:v>
       </x:c>
       <x:c r="H27" s="2" t="str">
         <x:v>06793353-094e-48e1-b4bd-031f3a03fe19</x:v>
@@ -2027,7 +2027,7 @@
         <x:v>city-07-guangzhou-ChangFen.png</x:v>
       </x:c>
       <x:c r="G28" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-07-guangzhou/city-07-guangzhou-ChangFen.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-07-guangzhou/city-07-guangzhou-ChangFen.png</x:v>
       </x:c>
       <x:c r="H28" s="2" t="str">
         <x:v>7c7a9ee2-6c6b-4c31-abce-11ea2840f36c</x:v>
@@ -2064,7 +2064,7 @@
         <x:v>city-07-guangzhou-ChaShao.png</x:v>
       </x:c>
       <x:c r="G29" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-07-guangzhou/city-07-guangzhou-ChaShao.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-07-guangzhou/city-07-guangzhou-ChaShao.png</x:v>
       </x:c>
       <x:c r="H29" s="2" t="str">
         <x:v>7b914314-9684-406c-85be-3ccd74d8592b</x:v>
@@ -2099,7 +2099,7 @@
         <x:v>city-07-guangzhou-GanChaoNiuHe.png</x:v>
       </x:c>
       <x:c r="G30" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-07-guangzhou/city-07-guangzhou-GanChaoNiuHe.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-07-guangzhou/city-07-guangzhou-GanChaoNiuHe.png</x:v>
       </x:c>
       <x:c r="H30" s="2" t="str">
         <x:v>69abb585-c79d-4d5a-b780-3695b93716be</x:v>
@@ -2134,7 +2134,7 @@
         <x:v>city-07-guangzhou-TingZaiZhou.png</x:v>
       </x:c>
       <x:c r="G31" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-07-guangzhou/city-07-guangzhou-TingZaiZhou.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-07-guangzhou/city-07-guangzhou-TingZaiZhou.png</x:v>
       </x:c>
       <x:c r="H31" s="2" t="str">
         <x:v>2428cd07-bcaa-43c5-ab53-7c1e49bf5bcf</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>city-08-chengdu-HuiGuoRou.png</x:v>
       </x:c>
       <x:c r="G32" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-08-chengdu/city-08-chengdu-HuiGuoRou.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-08-chengdu/city-08-chengdu-HuiGuoRou.png</x:v>
       </x:c>
       <x:c r="H32" s="2" t="str">
         <x:v>3d761d6b-f995-4eb2-8b1c-ee33ac328f8d</x:v>
@@ -2210,7 +2210,7 @@
         <x:v>city-08-chengdu-FuQiFeiPian.png</x:v>
       </x:c>
       <x:c r="G33" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-08-chengdu/city-08-chengdu-FuQiFeiPian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-08-chengdu/city-08-chengdu-FuQiFeiPian.png</x:v>
       </x:c>
       <x:c r="H33" s="2" t="str">
         <x:v>3d6be629-f92e-49bc-af5a-15263f553e49</x:v>
@@ -2249,7 +2249,7 @@
         <x:v>city-08-chengdu-MaPoDouFu.png</x:v>
       </x:c>
       <x:c r="G34" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-08-chengdu/city-08-chengdu-MaPoDouFu.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-08-chengdu/city-08-chengdu-MaPoDouFu.png</x:v>
       </x:c>
       <x:c r="H34" s="2" t="str">
         <x:v>edd4649b-e09c-4922-b431-7525b5dac15b</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>city-08-chengdu-DanDanMian.png</x:v>
       </x:c>
       <x:c r="G35" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-08-chengdu/city-08-chengdu-DanDanMian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-08-chengdu/city-08-chengdu-DanDanMian.png</x:v>
       </x:c>
       <x:c r="H35" s="2" t="str">
         <x:v>02e5f9cf-20e3-40b9-bcee-9ffb0ca1283e</x:v>
@@ -2327,7 +2327,7 @@
         <x:v>city-08-chengdu-LongChaoShou.png</x:v>
       </x:c>
       <x:c r="G36" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-08-chengdu/city-08-chengdu-LongChaoShou.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-08-chengdu/city-08-chengdu-LongChaoShou.png</x:v>
       </x:c>
       <x:c r="H36" s="2" t="str">
         <x:v>a43d8fd8-f1d0-4125-9073-a0aa0a95433a</x:v>
@@ -2366,7 +2366,7 @@
         <x:v>city-09-xian-NiuYangRouPaoMo.png</x:v>
       </x:c>
       <x:c r="G37" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-09-xian/city-09-xian-NiuYangRouPaoMo.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-09-xian/city-09-xian-NiuYangRouPaoMo.png</x:v>
       </x:c>
       <x:c r="H37" s="2" t="str">
         <x:v>d8befafb-0f4a-4434-a32f-e5a70836f24c</x:v>
@@ -2405,7 +2405,7 @@
         <x:v>city-09-xian-RouWanHuLaTang.png</x:v>
       </x:c>
       <x:c r="G38" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-09-xian/city-09-xian-RouWanHuLaTang.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-09-xian/city-09-xian-RouWanHuLaTang.png</x:v>
       </x:c>
       <x:c r="H38" s="2" t="str">
         <x:v>506e3e46-5a6d-49d5-8d12-a05e2a9bf6d5</x:v>
@@ -2444,7 +2444,7 @@
         <x:v>city-09-xian-RouJiaMo.png</x:v>
       </x:c>
       <x:c r="G39" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-09-xian/city-09-xian-RouJiaMo.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-09-xian/city-09-xian-RouJiaMo.png</x:v>
       </x:c>
       <x:c r="H39" s="2" t="str">
         <x:v>fbaf427b-0275-4359-b9bd-94d28928ee7d</x:v>
@@ -2483,7 +2483,7 @@
         <x:v>city-09-xian-HuLuJi.png</x:v>
       </x:c>
       <x:c r="G40" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-09-xian/city-09-xian-HuLuJi.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-09-xian/city-09-xian-HuLuJi.png</x:v>
       </x:c>
       <x:c r="H40" s="2" t="str">
         <x:v>2a59dff9-758c-433d-96ee-5fe05f0bb6ff</x:v>
@@ -2522,7 +2522,7 @@
         <x:v>city-09-xian-BiangbiangMian.png</x:v>
       </x:c>
       <x:c r="G41" s="2" t="str">
-        <x:v>assets/Bundle/thumbnails/city-09-xian/city-09-xian-BiangbiangMian.png</x:v>
+        <x:v>assets/Bundle/food-icons/city-09-xian/city-09-xian-BiangbiangMian.png</x:v>
       </x:c>
       <x:c r="H41" s="2" t="str">
         <x:v>2202379f-b9b0-4c3d-aab2-5aab32ac8e70</x:v>
@@ -2542,7 +2542,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb64f489755c34bb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b84affa55c64c71"/>
   </x:tableParts>
 </x:worksheet>
 </file>